--- a/engineer_forms/005_dam_inspection_form--engineer_forms.xlsx
+++ b/engineer_forms/005_dam_inspection_form--engineer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inspection Frequency</t>
+          <t>Inspector Frequency</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>spillway_status</t>
+          <t>spillway_status_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spillway Status</t>
+          <t>Spillway Status 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dam_condition</t>
+          <t>dam_condition_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dam Condition</t>
+          <t>Dam Condition 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>inspection_results</t>
+          <t>inspection_results_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inspection Results</t>
+          <t>Inspection Results 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'dam_prophets'}</t>
+          <t>dam_prophets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Dam prophets'}</t>
+          <t>Dam prophets</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'dam_gates'}</t>
+          <t>dam_gates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Dam gates'}</t>
+          <t>Dam gates</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'dam_spillway'}</t>
+          <t>dam_spillway</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Dam spillway'}</t>
+          <t>Dam spillway</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'engineer'}</t>
+          <t>engineer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Engineer'}</t>
+          <t>Engineer</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'above_water'}</t>
+          <t>above_water</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'Above Water'}</t>
+          <t>Above Water</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'below_water'}</t>
+          <t>below_water</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'Below Water'}</t>
+          <t>Below Water</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'on_water'}</t>
+          <t>on_water</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'On Water'}</t>
+          <t>On Water</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'in_use'}</t>
+          <t>in_use</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'In Use'}</t>
+          <t>In Use</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'bi-monthly'}</t>
+          <t>bi-monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'Bi-Monthly'}</t>
+          <t>Bi-Monthly</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_'bi-monthly'}</t>
+          <t>bi-monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 'Bi-Monthly'}</t>
+          <t>Bi-Monthly</t>
         </is>
       </c>
     </row>
@@ -1333,19 +1333,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>spillway_status_choices</t>
+          <t>spillway_status_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1362,7 +1362,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>spillway_status_choices</t>
+          <t>spillway_status_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dam_condition_choices</t>
+          <t>dam_condition_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dam_condition_choices</t>
+          <t>dam_condition_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
